--- a/lab-standards/BEIOA-lab-standard.xlsx
+++ b/lab-standards/BEIOA-lab-standard.xlsx
@@ -562,6 +562,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -575,6 +579,10 @@
 CNC Workshop : 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -644,7 +652,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -666,7 +676,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -688,7 +700,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -710,7 +724,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -732,7 +748,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -754,7 +772,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -776,7 +796,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -798,7 +820,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -820,7 +844,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -966,6 +992,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -979,6 +1009,10 @@
 Workshop : 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1048,7 +1082,9 @@
       <c r="C16" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -1070,7 +1106,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -1092,7 +1130,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -1114,7 +1154,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1136,7 +1178,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -1158,7 +1202,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1180,7 +1226,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -1202,7 +1250,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -1224,7 +1274,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -1246,7 +1298,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1392,6 +1446,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1405,6 +1463,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1474,7 +1536,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1496,7 +1560,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1518,7 +1584,9 @@
       <c r="C18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -1540,7 +1608,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -1562,7 +1632,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -1584,7 +1656,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1606,7 +1680,9 @@
       <c r="C22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -1628,7 +1704,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -1650,7 +1728,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -1672,7 +1752,9 @@
       <c r="C25" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1694,7 +1776,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -1716,7 +1800,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -1738,7 +1824,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -1760,7 +1848,9 @@
       <c r="C29" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -1782,7 +1872,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -1804,7 +1896,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -1826,7 +1920,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1848,7 +1944,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1870,7 +1968,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -1892,7 +1992,9 @@
       <c r="C35" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>6</v>
       </c>
@@ -1914,7 +2016,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -1936,7 +2040,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -1958,7 +2064,9 @@
       <c r="C38" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -1980,7 +2088,9 @@
       <c r="C39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
@@ -2002,7 +2112,9 @@
       <c r="C40" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -2024,7 +2136,9 @@
       <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>5</v>
       </c>
@@ -2046,7 +2160,9 @@
       <c r="C42" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>6</v>
       </c>
@@ -2068,7 +2184,9 @@
       <c r="C43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>5</v>
       </c>
@@ -2090,7 +2208,9 @@
       <c r="C44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>7</v>
       </c>
@@ -2112,7 +2232,9 @@
       <c r="C45" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>8</v>
       </c>
@@ -2134,7 +2256,9 @@
       <c r="C46" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>4</v>
       </c>
@@ -2156,7 +2280,9 @@
       <c r="C47" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="9" t="n">
         <v>3</v>
       </c>
@@ -2178,7 +2304,9 @@
       <c r="C48" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="9" t="n"/>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="9" t="n">
         <v>4</v>
       </c>
@@ -2324,6 +2452,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2337,6 +2469,10 @@
 Workshop/Lab : 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2406,7 +2542,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -2428,7 +2566,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -2450,7 +2590,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -2472,7 +2614,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -2494,7 +2638,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -2516,7 +2662,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -2538,7 +2686,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -2560,7 +2710,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2582,7 +2734,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2604,7 +2758,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -2626,7 +2782,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -2648,7 +2806,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -2670,7 +2830,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -2692,7 +2854,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -2714,7 +2878,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -2736,7 +2902,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -2758,7 +2926,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>8</v>
       </c>
@@ -2780,7 +2950,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -2926,6 +3098,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2939,6 +3115,10 @@
 Workshop/ Lab : 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3008,7 +3188,9 @@
       <c r="C16" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -3030,7 +3212,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -3052,7 +3236,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -3074,7 +3260,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -3096,7 +3284,9 @@
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -3118,7 +3308,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -3140,7 +3332,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -3162,7 +3356,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -3184,7 +3380,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -3330,6 +3528,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3344,6 +3546,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3413,7 +3619,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3435,7 +3643,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3457,7 +3667,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3479,7 +3691,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -3501,7 +3715,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3523,7 +3739,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -3545,7 +3763,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -3567,7 +3787,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3589,7 +3811,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -3611,7 +3835,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -3633,7 +3859,9 @@
       <c r="C26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3655,7 +3883,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -3677,7 +3907,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -3699,7 +3931,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -3721,7 +3955,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -3743,7 +3979,9 @@
       <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -3889,6 +4127,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3902,6 +4144,10 @@
 Workshop : 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3971,7 +4217,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -3993,7 +4241,9 @@
       <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -4015,7 +4265,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -4037,7 +4289,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -4059,7 +4313,9 @@
       <c r="C20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -4081,7 +4337,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -4103,7 +4361,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -4125,7 +4385,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -4147,7 +4409,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -4169,7 +4433,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -4191,7 +4457,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -4213,7 +4481,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -4235,7 +4505,9 @@
       <c r="C28" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -4257,7 +4529,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -4279,7 +4553,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -4301,7 +4577,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -4323,7 +4601,9 @@
       <c r="C32" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -4345,7 +4625,9 @@
       <c r="C33" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -4367,7 +4649,9 @@
       <c r="C34" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -4389,7 +4673,9 @@
       <c r="C35" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>5</v>
       </c>
@@ -4411,7 +4697,9 @@
       <c r="C36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -4433,7 +4721,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -4455,7 +4745,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -4477,7 +4769,9 @@
       <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>7</v>
       </c>
@@ -4499,7 +4793,9 @@
       <c r="C40" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>5</v>
       </c>
@@ -4521,7 +4817,9 @@
       <c r="C41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>5</v>
       </c>
@@ -4543,7 +4841,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>6</v>
       </c>
@@ -4565,7 +4865,9 @@
       <c r="C43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>6</v>
       </c>
@@ -4587,7 +4889,9 @@
       <c r="C44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>5</v>
       </c>

--- a/lab-standards/BEIOA-lab-standard.xlsx
+++ b/lab-standards/BEIOA-lab-standard.xlsx
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F37" s="9">
         <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="9">
         <f>IFERROR(MIN(C41,D41)*E41/C41,0)</f>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" s="9">
         <f>IFERROR(MIN(C42,D42)*E42/C42,0)</f>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F45" s="9">
         <f>IFERROR(MIN(C45,D45)*E45/C45,0)</f>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -2786,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>

--- a/lab-standards/BEIOA-lab-standard.xlsx
+++ b/lab-standards/BEIOA-lab-standard.xlsx
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>

--- a/lab-standards/BEIOA-lab-standard.xlsx
+++ b/lab-standards/BEIOA-lab-standard.xlsx
@@ -3695,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
